--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W418"/>
+  <dimension ref="A1:W420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31576,16 +31576,16 @@
         <v>335.35</v>
       </c>
       <c r="C418" t="n">
-        <v>322.82</v>
+        <v>294.78</v>
       </c>
       <c r="D418" t="n">
-        <v>331.2</v>
+        <v>307.94</v>
       </c>
       <c r="E418" t="n">
-        <v>316.15</v>
+        <v>295.56</v>
       </c>
       <c r="F418" t="n">
-        <v>295.69</v>
+        <v>280.34</v>
       </c>
       <c r="G418" t="n">
         <v>313.55</v>
@@ -31594,7 +31594,7 @@
         <v>310.28</v>
       </c>
       <c r="I418" t="n">
-        <v>292.99</v>
+        <v>281.34</v>
       </c>
       <c r="J418" t="n">
         <v>275.95</v>
@@ -31636,6 +31636,156 @@
         <v>287.48</v>
       </c>
       <c r="W418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="C419" t="n">
+        <v>276.96</v>
+      </c>
+      <c r="D419" t="n">
+        <v>293.29</v>
+      </c>
+      <c r="E419" t="n">
+        <v>282.22</v>
+      </c>
+      <c r="F419" t="n">
+        <v>270.76</v>
+      </c>
+      <c r="G419" t="n">
+        <v>302.25</v>
+      </c>
+      <c r="H419" t="n">
+        <v>303.13</v>
+      </c>
+      <c r="I419" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="J419" t="n">
+        <v>271.04</v>
+      </c>
+      <c r="K419" t="n">
+        <v>283.03</v>
+      </c>
+      <c r="L419" t="n">
+        <v>283.72</v>
+      </c>
+      <c r="M419" t="n">
+        <v>319.51</v>
+      </c>
+      <c r="N419" t="n">
+        <v>322.14</v>
+      </c>
+      <c r="O419" t="n">
+        <v>312.8</v>
+      </c>
+      <c r="P419" t="n">
+        <v>320.5</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>334.56</v>
+      </c>
+      <c r="R419" t="n">
+        <v>339.77</v>
+      </c>
+      <c r="S419" t="n">
+        <v>353.95</v>
+      </c>
+      <c r="T419" t="n">
+        <v>348.1</v>
+      </c>
+      <c r="U419" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="V419" t="n">
+        <v>271.42</v>
+      </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="C420" t="n">
+        <v>265.09</v>
+      </c>
+      <c r="D420" t="n">
+        <v>283.53</v>
+      </c>
+      <c r="E420" t="n">
+        <v>273.24</v>
+      </c>
+      <c r="F420" t="n">
+        <v>264.54</v>
+      </c>
+      <c r="G420" t="n">
+        <v>294.03</v>
+      </c>
+      <c r="H420" t="n">
+        <v>303.13</v>
+      </c>
+      <c r="I420" t="n">
+        <v>271.08</v>
+      </c>
+      <c r="J420" t="n">
+        <v>268.16</v>
+      </c>
+      <c r="K420" t="n">
+        <v>281.25</v>
+      </c>
+      <c r="L420" t="n">
+        <v>281.46</v>
+      </c>
+      <c r="M420" t="n">
+        <v>320.64</v>
+      </c>
+      <c r="N420" t="n">
+        <v>323.23</v>
+      </c>
+      <c r="O420" t="n">
+        <v>311.82</v>
+      </c>
+      <c r="P420" t="n">
+        <v>321.63</v>
+      </c>
+      <c r="Q420" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="R420" t="n">
+        <v>341.73</v>
+      </c>
+      <c r="S420" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="T420" t="n">
+        <v>350.03</v>
+      </c>
+      <c r="U420" t="n">
+        <v>343.29</v>
+      </c>
+      <c r="V420" t="n">
+        <v>259.05</v>
+      </c>
+      <c r="W420" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31652,7 +31802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B454"/>
+  <dimension ref="A1:B456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36195,6 +36345,26 @@
       </c>
       <c r="B454" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -36363,28 +36533,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.300405528219557</v>
+        <v>-0.2915498817028942</v>
       </c>
       <c r="J2" t="n">
+        <v>419</v>
+      </c>
+      <c r="K2" t="n">
         <v>417</v>
       </c>
-      <c r="K2" t="n">
-        <v>415</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01738796056046255</v>
+        <v>0.01653722941770175</v>
       </c>
       <c r="M2" t="n">
-        <v>11.70049575426821</v>
+        <v>11.67403923251064</v>
       </c>
       <c r="N2" t="n">
-        <v>247.2933558483419</v>
+        <v>246.493382067047</v>
       </c>
       <c r="O2" t="n">
-        <v>15.72556376885554</v>
+        <v>15.70010770877216</v>
       </c>
       <c r="P2" t="n">
-        <v>332.5720464516596</v>
+        <v>332.4676212219852</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36441,28 +36611,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.325880711600689</v>
+        <v>-0.3947616434447512</v>
       </c>
       <c r="J3" t="n">
+        <v>419</v>
+      </c>
+      <c r="K3" t="n">
         <v>417</v>
       </c>
-      <c r="K3" t="n">
-        <v>415</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.006895337464726037</v>
+        <v>0.009971160807861201</v>
       </c>
       <c r="M3" t="n">
-        <v>18.13888569570353</v>
+        <v>18.50002809816809</v>
       </c>
       <c r="N3" t="n">
-        <v>741.6858259788227</v>
+        <v>754.4950133480975</v>
       </c>
       <c r="O3" t="n">
-        <v>27.23390948760061</v>
+        <v>27.46807261800685</v>
       </c>
       <c r="P3" t="n">
-        <v>334.3185159776411</v>
+        <v>335.1305447035491</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36519,28 +36689,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.001165361846247</v>
+        <v>-1.049247718107672</v>
       </c>
       <c r="J4" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K4" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03694566118324571</v>
+        <v>0.04062656272586418</v>
       </c>
       <c r="M4" t="n">
-        <v>22.90735316993993</v>
+        <v>23.15357988804429</v>
       </c>
       <c r="N4" t="n">
-        <v>1267.81060199269</v>
+        <v>1268.580540883852</v>
       </c>
       <c r="O4" t="n">
-        <v>35.60632811724189</v>
+        <v>35.61713830284308</v>
       </c>
       <c r="P4" t="n">
-        <v>351.5367482713746</v>
+        <v>352.1028910283646</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36597,28 +36767,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.155102176239239</v>
+        <v>-2.176611556091946</v>
       </c>
       <c r="J5" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K5" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0935968253574837</v>
+        <v>0.09624465305996799</v>
       </c>
       <c r="M5" t="n">
-        <v>34.72523887625047</v>
+        <v>34.60980872057595</v>
       </c>
       <c r="N5" t="n">
-        <v>2248.303442585077</v>
+        <v>2236.147786051144</v>
       </c>
       <c r="O5" t="n">
-        <v>47.41627824476608</v>
+        <v>47.28792431531695</v>
       </c>
       <c r="P5" t="n">
-        <v>346.5200045561626</v>
+        <v>346.7696097741347</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36675,28 +36845,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7851073489068791</v>
+        <v>-0.824373737661007</v>
       </c>
       <c r="J6" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K6" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01671716919314359</v>
+        <v>0.01852955517344912</v>
       </c>
       <c r="M6" t="n">
-        <v>31.91439314118885</v>
+        <v>32.00207447204406</v>
       </c>
       <c r="N6" t="n">
-        <v>1787.703258259037</v>
+        <v>1784.579401786986</v>
       </c>
       <c r="O6" t="n">
-        <v>42.28124002745233</v>
+        <v>42.24428247451939</v>
       </c>
       <c r="P6" t="n">
-        <v>320.1606793623088</v>
+        <v>320.6213809487124</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36753,28 +36923,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9044399603612946</v>
+        <v>-0.9072398826753429</v>
       </c>
       <c r="J7" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K7" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05324697119824695</v>
+        <v>0.05409254233569349</v>
       </c>
       <c r="M7" t="n">
-        <v>19.92574618607618</v>
+        <v>19.85147652249207</v>
       </c>
       <c r="N7" t="n">
-        <v>709.173620073968</v>
+        <v>705.7728347640498</v>
       </c>
       <c r="O7" t="n">
-        <v>26.63031393119443</v>
+        <v>26.56638542903513</v>
       </c>
       <c r="P7" t="n">
-        <v>325.069838267509</v>
+        <v>325.1028666737296</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36831,28 +37001,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1098041676638907</v>
+        <v>-0.1136923895807405</v>
       </c>
       <c r="J8" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K8" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00167212971594255</v>
+        <v>0.001810612885656759</v>
       </c>
       <c r="M8" t="n">
-        <v>15.07584199424666</v>
+        <v>15.02688719094303</v>
       </c>
       <c r="N8" t="n">
-        <v>355.0240140972384</v>
+        <v>353.3853660605315</v>
       </c>
       <c r="O8" t="n">
-        <v>18.84208093861287</v>
+        <v>18.79854691353913</v>
       </c>
       <c r="P8" t="n">
-        <v>309.9731033067077</v>
+        <v>310.0185895893254</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36909,28 +37079,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.714277007556309</v>
+        <v>-0.7300103202266507</v>
       </c>
       <c r="J9" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K9" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02746869291787835</v>
+        <v>0.02893965149821065</v>
       </c>
       <c r="M9" t="n">
-        <v>25.05021005069874</v>
+        <v>24.95424974539426</v>
       </c>
       <c r="N9" t="n">
-        <v>902.9578146923028</v>
+        <v>898.7745868371924</v>
       </c>
       <c r="O9" t="n">
-        <v>30.04925647486644</v>
+        <v>29.97956949052458</v>
       </c>
       <c r="P9" t="n">
-        <v>302.0551379440494</v>
+        <v>302.2379127022999</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36987,28 +37157,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6340702855700064</v>
+        <v>-0.6406062896276631</v>
       </c>
       <c r="J10" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K10" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01755208262200825</v>
+        <v>0.01808894539641781</v>
       </c>
       <c r="M10" t="n">
-        <v>27.92247783733353</v>
+        <v>27.81869320159322</v>
       </c>
       <c r="N10" t="n">
-        <v>1111.0638657124</v>
+        <v>1105.909776155468</v>
       </c>
       <c r="O10" t="n">
-        <v>33.33262464481907</v>
+        <v>33.25522178779548</v>
       </c>
       <c r="P10" t="n">
-        <v>293.1272407224399</v>
+        <v>293.2036323491063</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37065,28 +37235,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2877100225306879</v>
+        <v>-0.2934689789988663</v>
       </c>
       <c r="J11" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K11" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01151397629818673</v>
+        <v>0.01209286368515439</v>
       </c>
       <c r="M11" t="n">
-        <v>15.54206387118765</v>
+        <v>15.49413888754233</v>
       </c>
       <c r="N11" t="n">
-        <v>350.7155129153826</v>
+        <v>349.1690763869895</v>
       </c>
       <c r="O11" t="n">
-        <v>18.72740005754623</v>
+        <v>18.68606637007879</v>
       </c>
       <c r="P11" t="n">
-        <v>295.5632264078133</v>
+        <v>295.6305072125907</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37143,28 +37313,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3233796224708888</v>
+        <v>-0.3287229583961858</v>
       </c>
       <c r="J12" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K12" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01117909412037676</v>
+        <v>0.01166315300193843</v>
       </c>
       <c r="M12" t="n">
-        <v>17.92495511395435</v>
+        <v>17.86505154382192</v>
       </c>
       <c r="N12" t="n">
-        <v>460.8801104893334</v>
+        <v>458.7854770340729</v>
       </c>
       <c r="O12" t="n">
-        <v>21.46811846644539</v>
+        <v>21.41927816323587</v>
       </c>
       <c r="P12" t="n">
-        <v>296.5955035226898</v>
+        <v>296.6575776097127</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37221,28 +37391,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4449611011973784</v>
+        <v>0.452782251144739</v>
       </c>
       <c r="J13" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K13" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04762230313039073</v>
+        <v>0.04964253877820002</v>
       </c>
       <c r="M13" t="n">
-        <v>11.27641051290209</v>
+        <v>11.26118835362655</v>
       </c>
       <c r="N13" t="n">
-        <v>194.2482418252254</v>
+        <v>193.6130081072393</v>
       </c>
       <c r="O13" t="n">
-        <v>13.93729679045493</v>
+        <v>13.9144891428769</v>
       </c>
       <c r="P13" t="n">
-        <v>300.2960405455118</v>
+        <v>300.2044682205063</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37299,28 +37469,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3484513775164911</v>
+        <v>0.3599505079839354</v>
       </c>
       <c r="J14" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K14" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0260056173550588</v>
+        <v>0.02790511359335435</v>
       </c>
       <c r="M14" t="n">
-        <v>11.77312397322672</v>
+        <v>11.76883157568329</v>
       </c>
       <c r="N14" t="n">
-        <v>223.5890467894696</v>
+        <v>223.1493820424753</v>
       </c>
       <c r="O14" t="n">
-        <v>14.95289426129502</v>
+        <v>14.93818536645182</v>
       </c>
       <c r="P14" t="n">
-        <v>301.802038995794</v>
+        <v>301.6675566962401</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37377,28 +37547,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01151411875232105</v>
+        <v>0.03035133925196755</v>
       </c>
       <c r="J15" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K15" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L15" t="n">
-        <v>1.924774781270067e-05</v>
+        <v>0.0001344495654593825</v>
       </c>
       <c r="M15" t="n">
-        <v>14.45041650364988</v>
+        <v>14.46856384232001</v>
       </c>
       <c r="N15" t="n">
-        <v>340.1500951960289</v>
+        <v>340.2074310472187</v>
       </c>
       <c r="O15" t="n">
-        <v>18.44315849294878</v>
+        <v>18.44471282094733</v>
       </c>
       <c r="P15" t="n">
-        <v>293.1030618640718</v>
+        <v>292.8832701579763</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37455,28 +37625,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03438938229541263</v>
+        <v>0.03954156071168523</v>
       </c>
       <c r="J16" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K16" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0003333407773919994</v>
+        <v>0.0004448942762516062</v>
       </c>
       <c r="M16" t="n">
-        <v>9.855984647677666</v>
+        <v>9.830574689523699</v>
       </c>
       <c r="N16" t="n">
-        <v>173.6060191761424</v>
+        <v>172.8989097638992</v>
       </c>
       <c r="O16" t="n">
-        <v>13.17596369060504</v>
+        <v>13.14910300225453</v>
       </c>
       <c r="P16" t="n">
-        <v>314.9877388152279</v>
+        <v>314.927198725446</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37533,28 +37703,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04871081845820989</v>
+        <v>0.05846373719907999</v>
       </c>
       <c r="J17" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K17" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0009270263921655753</v>
+        <v>0.001343838262000463</v>
       </c>
       <c r="M17" t="n">
-        <v>8.508886963611321</v>
+        <v>8.519417843154356</v>
       </c>
       <c r="N17" t="n">
-        <v>125.4498506486681</v>
+        <v>125.303981117982</v>
       </c>
       <c r="O17" t="n">
-        <v>11.20043975246812</v>
+        <v>11.19392608149536</v>
       </c>
       <c r="P17" t="n">
-        <v>323.9498423209298</v>
+        <v>323.8356542761348</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37611,28 +37781,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.01892710121576555</v>
+        <v>-0.00784402461470165</v>
       </c>
       <c r="J18" t="n">
+        <v>419</v>
+      </c>
+      <c r="K18" t="n">
         <v>417</v>
       </c>
-      <c r="K18" t="n">
-        <v>415</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.0001820039885953584</v>
+        <v>3.139665783169487e-05</v>
       </c>
       <c r="M18" t="n">
-        <v>7.459014626335931</v>
+        <v>7.478786222447831</v>
       </c>
       <c r="N18" t="n">
-        <v>96.44375666218697</v>
+        <v>96.56930922057606</v>
       </c>
       <c r="O18" t="n">
-        <v>9.82057822443195</v>
+        <v>9.826968465431039</v>
       </c>
       <c r="P18" t="n">
-        <v>330.144335575281</v>
+        <v>330.014293570264</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37689,28 +37859,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1296880180991748</v>
+        <v>-0.1161365857248325</v>
       </c>
       <c r="J19" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K19" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L19" t="n">
-        <v>0.006403409829432549</v>
+        <v>0.005159387524111159</v>
       </c>
       <c r="M19" t="n">
-        <v>8.847238113851374</v>
+        <v>8.862173826560198</v>
       </c>
       <c r="N19" t="n">
-        <v>128.0302765486075</v>
+        <v>128.2969122231117</v>
       </c>
       <c r="O19" t="n">
-        <v>11.31504646692215</v>
+        <v>11.32682268878222</v>
       </c>
       <c r="P19" t="n">
-        <v>344.8931495708706</v>
+        <v>344.7344840816909</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37767,28 +37937,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1467789548300554</v>
+        <v>0.1509657207923907</v>
       </c>
       <c r="J20" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K20" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008109672061900497</v>
+        <v>0.008657321925545469</v>
       </c>
       <c r="M20" t="n">
-        <v>8.398886799024055</v>
+        <v>8.376209277450174</v>
       </c>
       <c r="N20" t="n">
-        <v>129.2713032847167</v>
+        <v>128.7418260241055</v>
       </c>
       <c r="O20" t="n">
-        <v>11.3697538796896</v>
+        <v>11.34644552377992</v>
       </c>
       <c r="P20" t="n">
-        <v>340.9269504628899</v>
+        <v>340.8779238419573</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37845,28 +38015,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3170389925773482</v>
+        <v>-0.3136511936674829</v>
       </c>
       <c r="J21" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K21" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03161618865231175</v>
+        <v>0.03126523249708457</v>
       </c>
       <c r="M21" t="n">
-        <v>9.069001940861174</v>
+        <v>9.039665180354033</v>
       </c>
       <c r="N21" t="n">
-        <v>150.74509797473</v>
+        <v>150.0791120291535</v>
       </c>
       <c r="O21" t="n">
-        <v>12.27782953028466</v>
+        <v>12.25067802324237</v>
       </c>
       <c r="P21" t="n">
-        <v>347.9596878237667</v>
+        <v>347.9199483510405</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37923,28 +38093,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1437077294851834</v>
+        <v>-0.2121518347119505</v>
       </c>
       <c r="J22" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K22" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L22" t="n">
-        <v>0.005512957202853608</v>
+        <v>0.01074998388773563</v>
       </c>
       <c r="M22" t="n">
-        <v>9.630276255003416</v>
+        <v>9.986263736715539</v>
       </c>
       <c r="N22" t="n">
-        <v>182.4125006429797</v>
+        <v>203.9271146941749</v>
       </c>
       <c r="O22" t="n">
-        <v>13.50601720134325</v>
+        <v>14.28030513309064</v>
       </c>
       <c r="P22" t="n">
-        <v>337.7265255337595</v>
+        <v>338.5293609565659</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37982,7 +38152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W418"/>
+  <dimension ref="A1:W420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86423,22 +86593,22 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>-37.68477372344251,174.8116560805212</t>
+          <t>-37.684680018197916,174.81195132222015</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>-37.68413834919645,174.811244865072</t>
+          <t>-37.68406061865456,174.8114897750293</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>-37.68342467061607,174.81108034912285</t>
+          <t>-37.68335586286739,174.81129714406063</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>-37.68269290741286,174.81097279262835</t>
+          <t>-37.682641610776244,174.81113441335773</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -86453,7 +86623,7 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>-37.68069609015102,174.81003691977776</t>
+          <t>-37.68065775018656,174.81015987469945</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -86522,6 +86692,240 @@
         </is>
       </c>
       <c r="W418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-37.685478969378394,174.8118471274738</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-37.684620466201565,174.8121389540273</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-37.684011660857124,174.8116440280198</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-37.683311282991475,174.81143760253147</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-37.68260959621847,174.8112352814226</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-37.68205143360242,174.81058073996337</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-37.68139180157687,174.8102489021259</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-37.68063655619537,174.81022784285742</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-37.679960092718645,174.80995364937914</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-37.67933372484291,174.8095111709014</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-37.67867039736666,174.8091880677771</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-37.67812184606375,174.80849416994332</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-37.67746484988408,174.80815057599764</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-37.67677529529447,174.80793652070892</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-37.676136314979864,174.80757256467353</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-37.675499104016815,174.80716179161215</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>-37.67483289019692,174.8068447128765</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>-37.67419107644021,174.8064306950661</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>-37.673492796689615,174.80623241901074</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>-37.672797175701554,174.80599033533514</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>-37.67186541379226,174.80631976746804</t>
+        </is>
+      </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-37.68546550176541,174.81188956099882</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-37.68458079812754,174.81226393643362</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-37.68397904449501,174.81174679303558</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-37.683281273357814,174.81153215393786</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-37.682588810103525,174.81130077191352</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-37.68202396424494,174.81066728805973</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-37.68139180157687,174.8102489021259</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-37.68062398458624,174.81026815935456</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-37.67995067443674,174.8099840741992</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-37.67932790387739,174.8095299750038</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-37.67866300674832,174.8092119424616</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-37.67812554131134,174.80848223265443</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-37.67746841430219,174.8081390613556</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-37.67677223230819,174.8079469409161</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-37.67613953629407,174.80756041229822</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-37.67550179775952,174.8071510923811</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>-37.674838223218764,174.80682353072908</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>-37.67419698078983,174.8064072435741</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>-37.673498415425634,174.80621171351493</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>-37.67280019537504,174.80598148014965</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>-37.671816018361795,174.80644547183314</t>
+        </is>
+      </c>
+      <c r="W420" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W420"/>
+  <dimension ref="A1:W421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31741,7 +31741,7 @@
         <v>294.03</v>
       </c>
       <c r="H420" t="n">
-        <v>303.13</v>
+        <v>302.23</v>
       </c>
       <c r="I420" t="n">
         <v>271.08</v>
@@ -31786,6 +31786,81 @@
         <v>259.05</v>
       </c>
       <c r="W420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>323.45</v>
+      </c>
+      <c r="C421" t="n">
+        <v>250.34</v>
+      </c>
+      <c r="D421" t="n">
+        <v>276.37</v>
+      </c>
+      <c r="E421" t="n">
+        <v>266.76</v>
+      </c>
+      <c r="F421" t="n">
+        <v>253.59</v>
+      </c>
+      <c r="G421" t="n">
+        <v>276.16</v>
+      </c>
+      <c r="H421" t="n">
+        <v>288.15</v>
+      </c>
+      <c r="I421" t="n">
+        <v>252.87</v>
+      </c>
+      <c r="J421" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="K421" t="n">
+        <v>272.88</v>
+      </c>
+      <c r="L421" t="n">
+        <v>274.05</v>
+      </c>
+      <c r="M421" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="N421" t="n">
+        <v>322.5</v>
+      </c>
+      <c r="O421" t="n">
+        <v>302.73</v>
+      </c>
+      <c r="P421" t="n">
+        <v>314.31</v>
+      </c>
+      <c r="Q421" t="n">
+        <v>329.52</v>
+      </c>
+      <c r="R421" t="n">
+        <v>336.81</v>
+      </c>
+      <c r="S421" t="n">
+        <v>353.08</v>
+      </c>
+      <c r="T421" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="U421" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="V421" t="n">
+        <v>237.62</v>
+      </c>
+      <c r="W421" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31802,7 +31877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B456"/>
+  <dimension ref="A1:B457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36365,6 +36440,16 @@
       </c>
       <c r="B456" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
@@ -36533,28 +36618,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2915498817028942</v>
+        <v>-0.2921450361795612</v>
       </c>
       <c r="J2" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01653722941770175</v>
+        <v>0.01668898788094419</v>
       </c>
       <c r="M2" t="n">
-        <v>11.67403923251064</v>
+        <v>11.64975232394362</v>
       </c>
       <c r="N2" t="n">
-        <v>246.493382067047</v>
+        <v>245.906991877923</v>
       </c>
       <c r="O2" t="n">
-        <v>15.70010770877216</v>
+        <v>15.68142187041478</v>
       </c>
       <c r="P2" t="n">
-        <v>332.4676212219852</v>
+        <v>332.4746707207653</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36611,28 +36696,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3947616434447512</v>
+        <v>-0.432163758183844</v>
       </c>
       <c r="J3" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K3" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009971160807861201</v>
+        <v>0.01178618824108035</v>
       </c>
       <c r="M3" t="n">
-        <v>18.50002809816809</v>
+        <v>18.70316546880488</v>
       </c>
       <c r="N3" t="n">
-        <v>754.4950133480975</v>
+        <v>765.7503146871206</v>
       </c>
       <c r="O3" t="n">
-        <v>27.46807261800685</v>
+        <v>27.6721938900247</v>
       </c>
       <c r="P3" t="n">
-        <v>335.1305447035491</v>
+        <v>335.57356609138</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36689,28 +36774,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.049247718107672</v>
+        <v>-1.073175408584075</v>
       </c>
       <c r="J4" t="n">
+        <v>420</v>
+      </c>
+      <c r="K4" t="n">
         <v>419</v>
       </c>
-      <c r="K4" t="n">
-        <v>418</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04062656272586418</v>
+        <v>0.04246226828759936</v>
       </c>
       <c r="M4" t="n">
-        <v>23.15357988804429</v>
+        <v>23.29250653363857</v>
       </c>
       <c r="N4" t="n">
-        <v>1268.580540883852</v>
+        <v>1270.898665022773</v>
       </c>
       <c r="O4" t="n">
-        <v>35.61713830284308</v>
+        <v>35.64966570702695</v>
       </c>
       <c r="P4" t="n">
-        <v>352.1028910283646</v>
+        <v>352.3859851596488</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36767,28 +36852,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.176611556091946</v>
+        <v>-2.187480852360392</v>
       </c>
       <c r="J5" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K5" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09624465305996799</v>
+        <v>0.09753384990286307</v>
       </c>
       <c r="M5" t="n">
-        <v>34.60980872057595</v>
+        <v>34.60357945740719</v>
       </c>
       <c r="N5" t="n">
-        <v>2236.147786051144</v>
+        <v>2231.765841718575</v>
       </c>
       <c r="O5" t="n">
-        <v>47.28792431531695</v>
+        <v>47.24156900144802</v>
       </c>
       <c r="P5" t="n">
-        <v>346.7696097741347</v>
+        <v>346.8964430552114</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36845,28 +36930,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.824373737661007</v>
+        <v>-0.8469578151680544</v>
       </c>
       <c r="J6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K6" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01852955517344912</v>
+        <v>0.01958581981339647</v>
       </c>
       <c r="M6" t="n">
-        <v>32.00207447204406</v>
+        <v>32.06306771549044</v>
       </c>
       <c r="N6" t="n">
-        <v>1784.579401786986</v>
+        <v>1785.096361850697</v>
       </c>
       <c r="O6" t="n">
-        <v>42.24428247451939</v>
+        <v>42.25040073006051</v>
       </c>
       <c r="P6" t="n">
-        <v>320.6213809487124</v>
+        <v>320.8876452671429</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36923,28 +37008,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9072398826753429</v>
+        <v>-0.919942078767134</v>
       </c>
       <c r="J7" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K7" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05409254233569349</v>
+        <v>0.05570384310180709</v>
       </c>
       <c r="M7" t="n">
-        <v>19.85147652249207</v>
+        <v>19.88304339073258</v>
       </c>
       <c r="N7" t="n">
-        <v>705.7728347640498</v>
+        <v>705.5052131733299</v>
       </c>
       <c r="O7" t="n">
-        <v>26.56638542903513</v>
+        <v>26.56134810534529</v>
       </c>
       <c r="P7" t="n">
-        <v>325.1028666737296</v>
+        <v>325.253155317722</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37001,28 +37086,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1136923895807405</v>
+        <v>-0.123534783780252</v>
       </c>
       <c r="J8" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K8" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001810612885656759</v>
+        <v>0.002142840312551741</v>
       </c>
       <c r="M8" t="n">
-        <v>15.02688719094303</v>
+        <v>15.05001352823245</v>
       </c>
       <c r="N8" t="n">
-        <v>353.3853660605315</v>
+        <v>353.3980651410621</v>
       </c>
       <c r="O8" t="n">
-        <v>18.79854691353913</v>
+        <v>18.79888467811487</v>
       </c>
       <c r="P8" t="n">
-        <v>310.0185895893254</v>
+        <v>310.1342157611265</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37079,28 +37164,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7300103202266507</v>
+        <v>-0.7449321352250174</v>
       </c>
       <c r="J9" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K9" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02893965149821065</v>
+        <v>0.03018156069220035</v>
       </c>
       <c r="M9" t="n">
-        <v>24.95424974539426</v>
+        <v>24.96673439990882</v>
       </c>
       <c r="N9" t="n">
-        <v>898.7745868371924</v>
+        <v>898.7219121158072</v>
       </c>
       <c r="O9" t="n">
-        <v>29.97956949052458</v>
+        <v>29.97869096734891</v>
       </c>
       <c r="P9" t="n">
-        <v>302.2379127022999</v>
+        <v>302.412186559109</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37157,28 +37242,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6406062896276631</v>
+        <v>-0.6519656644559287</v>
       </c>
       <c r="J10" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K10" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01808894539641781</v>
+        <v>0.0187994529024037</v>
       </c>
       <c r="M10" t="n">
-        <v>27.81869320159322</v>
+        <v>27.80579319132985</v>
       </c>
       <c r="N10" t="n">
-        <v>1105.909776155468</v>
+        <v>1104.474528855399</v>
       </c>
       <c r="O10" t="n">
-        <v>33.25522178779548</v>
+        <v>33.23363550464197</v>
       </c>
       <c r="P10" t="n">
-        <v>293.2036323491063</v>
+        <v>293.3369529571122</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37235,28 +37320,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2934689789988663</v>
+        <v>-0.3009741637281641</v>
       </c>
       <c r="J11" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K11" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01209286368515439</v>
+        <v>0.01275833085259581</v>
       </c>
       <c r="M11" t="n">
-        <v>15.49413888754233</v>
+        <v>15.49217485322479</v>
       </c>
       <c r="N11" t="n">
-        <v>349.1690763869895</v>
+        <v>348.8529213651889</v>
       </c>
       <c r="O11" t="n">
-        <v>18.68606637007879</v>
+        <v>18.67760480803652</v>
       </c>
       <c r="P11" t="n">
-        <v>295.6305072125907</v>
+        <v>295.7185590926601</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37313,28 +37398,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3287229583961858</v>
+        <v>-0.335622877807994</v>
       </c>
       <c r="J12" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K12" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01166315300193843</v>
+        <v>0.01220294106563458</v>
       </c>
       <c r="M12" t="n">
-        <v>17.86505154382192</v>
+        <v>17.8563511227646</v>
       </c>
       <c r="N12" t="n">
-        <v>458.7854770340729</v>
+        <v>458.1301076626311</v>
       </c>
       <c r="O12" t="n">
-        <v>21.41927816323587</v>
+        <v>21.40397410909084</v>
       </c>
       <c r="P12" t="n">
-        <v>296.6575776097127</v>
+        <v>296.7380718514514</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37391,28 +37476,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.452782251144739</v>
+        <v>0.4553338840295929</v>
       </c>
       <c r="J13" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K13" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04964253877820002</v>
+        <v>0.05040845401523053</v>
       </c>
       <c r="M13" t="n">
-        <v>11.26118835362655</v>
+        <v>11.24682089234966</v>
       </c>
       <c r="N13" t="n">
-        <v>193.6130081072393</v>
+        <v>193.2138319593336</v>
       </c>
       <c r="O13" t="n">
-        <v>13.9144891428769</v>
+        <v>13.90013783958035</v>
       </c>
       <c r="P13" t="n">
-        <v>300.2044682205063</v>
+        <v>300.1744657504623</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37469,28 +37554,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3599505079839354</v>
+        <v>0.3655178620230281</v>
       </c>
       <c r="J14" t="n">
+        <v>420</v>
+      </c>
+      <c r="K14" t="n">
         <v>419</v>
       </c>
-      <c r="K14" t="n">
-        <v>418</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02790511359335435</v>
+        <v>0.02885855717535757</v>
       </c>
       <c r="M14" t="n">
-        <v>11.76883157568329</v>
+        <v>11.76573475019548</v>
       </c>
       <c r="N14" t="n">
-        <v>223.1493820424753</v>
+        <v>222.9113919748064</v>
       </c>
       <c r="O14" t="n">
-        <v>14.93818536645182</v>
+        <v>14.93021741217476</v>
       </c>
       <c r="P14" t="n">
-        <v>301.6675566962401</v>
+        <v>301.6021672326353</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37547,28 +37632,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03035133925196755</v>
+        <v>0.0348672476791829</v>
       </c>
       <c r="J15" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K15" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0001344495654593825</v>
+        <v>0.0001782526804818829</v>
       </c>
       <c r="M15" t="n">
-        <v>14.46856384232001</v>
+        <v>14.45478866387311</v>
       </c>
       <c r="N15" t="n">
-        <v>340.2074310472187</v>
+        <v>339.5858447644006</v>
       </c>
       <c r="O15" t="n">
-        <v>18.44471282094733</v>
+        <v>18.42785513195718</v>
       </c>
       <c r="P15" t="n">
-        <v>292.8832701579763</v>
+        <v>292.8303483032582</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37625,28 +37710,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03954156071168523</v>
+        <v>0.03869865266483985</v>
       </c>
       <c r="J16" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K16" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0004448942762516062</v>
+        <v>0.0004283359976539058</v>
       </c>
       <c r="M16" t="n">
-        <v>9.830574689523699</v>
+        <v>9.81146514312973</v>
       </c>
       <c r="N16" t="n">
-        <v>172.8989097638992</v>
+        <v>172.491024912149</v>
       </c>
       <c r="O16" t="n">
-        <v>13.14910300225453</v>
+        <v>13.13358385636415</v>
       </c>
       <c r="P16" t="n">
-        <v>314.927198725446</v>
+        <v>314.9371452731311</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37703,28 +37788,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.05846373719907999</v>
+        <v>0.06051466043777787</v>
       </c>
       <c r="J17" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K17" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001343838262000463</v>
+        <v>0.001446668328936473</v>
       </c>
       <c r="M17" t="n">
-        <v>8.519417843154356</v>
+        <v>8.50982696835162</v>
       </c>
       <c r="N17" t="n">
-        <v>125.303981117982</v>
+        <v>125.045568510228</v>
       </c>
       <c r="O17" t="n">
-        <v>11.19392608149536</v>
+        <v>11.18237758753603</v>
       </c>
       <c r="P17" t="n">
-        <v>323.8356542761348</v>
+        <v>323.8115392228303</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37781,28 +37866,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.00784402461470165</v>
+        <v>-0.00433867399170521</v>
       </c>
       <c r="J18" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K18" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L18" t="n">
-        <v>3.139665783169487e-05</v>
+        <v>9.644011813914055e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>7.478786222447831</v>
+        <v>7.478448585780516</v>
       </c>
       <c r="N18" t="n">
-        <v>96.56930922057606</v>
+        <v>96.45495435654801</v>
       </c>
       <c r="O18" t="n">
-        <v>9.826968465431039</v>
+        <v>9.821148321685607</v>
       </c>
       <c r="P18" t="n">
-        <v>330.014293570264</v>
+        <v>329.9729887705365</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37859,28 +37944,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1161365857248325</v>
+        <v>-0.1104127516031745</v>
       </c>
       <c r="J19" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K19" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L19" t="n">
-        <v>0.005159387524111159</v>
+        <v>0.004678554293586545</v>
       </c>
       <c r="M19" t="n">
-        <v>8.862173826560198</v>
+        <v>8.864901232927039</v>
       </c>
       <c r="N19" t="n">
-        <v>128.2969122231117</v>
+        <v>128.3024551367982</v>
       </c>
       <c r="O19" t="n">
-        <v>11.32682268878222</v>
+        <v>11.32706736701068</v>
       </c>
       <c r="P19" t="n">
-        <v>344.7344840816909</v>
+        <v>344.6671824087929</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37937,28 +38022,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1509657207923907</v>
+        <v>0.1525730318210455</v>
       </c>
       <c r="J20" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K20" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008657321925545469</v>
+        <v>0.008884993199697933</v>
       </c>
       <c r="M20" t="n">
-        <v>8.376209277450174</v>
+        <v>8.362862391048703</v>
       </c>
       <c r="N20" t="n">
-        <v>128.7418260241055</v>
+        <v>128.4598225029443</v>
       </c>
       <c r="O20" t="n">
-        <v>11.34644552377992</v>
+        <v>11.33401175678516</v>
       </c>
       <c r="P20" t="n">
-        <v>340.8779238419573</v>
+        <v>340.8590248454461</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -38015,28 +38100,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3136511936674829</v>
+        <v>-0.3144244935299608</v>
       </c>
       <c r="J21" t="n">
+        <v>420</v>
+      </c>
+      <c r="K21" t="n">
         <v>419</v>
       </c>
-      <c r="K21" t="n">
-        <v>418</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.03126523249708457</v>
+        <v>0.03157212027611778</v>
       </c>
       <c r="M21" t="n">
-        <v>9.039665180354033</v>
+        <v>9.022257876011896</v>
       </c>
       <c r="N21" t="n">
-        <v>150.0791120291535</v>
+        <v>149.7265939002657</v>
       </c>
       <c r="O21" t="n">
-        <v>12.25067802324237</v>
+        <v>12.23628186583922</v>
       </c>
       <c r="P21" t="n">
-        <v>347.9199483510405</v>
+        <v>347.9290574877379</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -38093,28 +38178,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2121518347119505</v>
+        <v>-0.259752804083208</v>
       </c>
       <c r="J22" t="n">
+        <v>420</v>
+      </c>
+      <c r="K22" t="n">
         <v>419</v>
       </c>
-      <c r="K22" t="n">
-        <v>418</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01074998388773563</v>
+        <v>0.01459588759788766</v>
       </c>
       <c r="M22" t="n">
-        <v>9.986263736715539</v>
+        <v>10.26447696623621</v>
       </c>
       <c r="N22" t="n">
-        <v>203.9271146941749</v>
+        <v>224.9090955658867</v>
       </c>
       <c r="O22" t="n">
-        <v>14.28030513309064</v>
+        <v>14.99696954607452</v>
       </c>
       <c r="P22" t="n">
-        <v>338.5293609565659</v>
+        <v>339.0900797125933</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -38152,7 +38237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W420"/>
+  <dimension ref="A1:W421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86852,7 +86937,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>-37.68139180157687,174.8102489021259</t>
+          <t>-37.68138880751485,174.81025838489577</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -86926,6 +87011,123 @@
         </is>
       </c>
       <c r="W420" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-37.68543920144593,174.81197242741501</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-37.68453150526895,174.81241924293866</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-37.68395511686227,174.81182218206578</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-37.683259618253246,174.81160038252065</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-37.68255221709779,174.8114160645669</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-37.681964246583526,174.8108554404452</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-37.68134196698111,174.81040673745983</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-37.68056405534297,174.81046034853594</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-37.67990207859646,174.8101410576929</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-37.679300532219386,174.80961839650072</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-37.67863877464362,174.8092902218131</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-37.67811527309831,174.808515403525</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-37.6774660271232,174.80814677299674</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-37.676743821504864,174.80804359361204</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-37.676118668997965,174.80763913386042</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-37.67548539040277,174.80721626041208</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>-37.674824836238486,174.80687670223597</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>-37.67418870925727,174.8064400972761</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>-37.6734929713654,174.8062317753166</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>-37.67278118918404,174.8060372157165</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>-37.67173044456345,174.80666324382523</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0216/nzd0216.xlsx
+++ b/data/nzd0216/nzd0216.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W421"/>
+  <dimension ref="A1:W422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31801,19 +31801,19 @@
         <v>323.45</v>
       </c>
       <c r="C421" t="n">
-        <v>250.34</v>
+        <v>259</v>
       </c>
       <c r="D421" t="n">
-        <v>276.37</v>
+        <v>283.92</v>
       </c>
       <c r="E421" t="n">
-        <v>266.76</v>
+        <v>273.23</v>
       </c>
       <c r="F421" t="n">
-        <v>253.59</v>
+        <v>260.62</v>
       </c>
       <c r="G421" t="n">
-        <v>276.16</v>
+        <v>280.38</v>
       </c>
       <c r="H421" t="n">
         <v>288.15</v>
@@ -31834,7 +31834,7 @@
         <v>317.5</v>
       </c>
       <c r="N421" t="n">
-        <v>322.5</v>
+        <v>319.14</v>
       </c>
       <c r="O421" t="n">
         <v>302.73</v>
@@ -31852,15 +31852,90 @@
         <v>353.08</v>
       </c>
       <c r="T421" t="n">
-        <v>348.16</v>
+        <v>345.83</v>
       </c>
       <c r="U421" t="n">
         <v>337.94</v>
       </c>
       <c r="V421" t="n">
-        <v>237.62</v>
+        <v>247.68</v>
       </c>
       <c r="W421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>317.13</v>
+      </c>
+      <c r="C422" t="n">
+        <v>253.11</v>
+      </c>
+      <c r="D422" t="n">
+        <v>281.1</v>
+      </c>
+      <c r="E422" t="n">
+        <v>272.24</v>
+      </c>
+      <c r="F422" t="n">
+        <v>257.98</v>
+      </c>
+      <c r="G422" t="n">
+        <v>280.22</v>
+      </c>
+      <c r="H422" t="n">
+        <v>288</v>
+      </c>
+      <c r="I422" t="n">
+        <v>244.96</v>
+      </c>
+      <c r="J422" t="n">
+        <v>247.36</v>
+      </c>
+      <c r="K422" t="n">
+        <v>271.82</v>
+      </c>
+      <c r="L422" t="n">
+        <v>271.46</v>
+      </c>
+      <c r="M422" t="n">
+        <v>314.08</v>
+      </c>
+      <c r="N422" t="n">
+        <v>314.24</v>
+      </c>
+      <c r="O422" t="n">
+        <v>299.71</v>
+      </c>
+      <c r="P422" t="n">
+        <v>311.9</v>
+      </c>
+      <c r="Q422" t="n">
+        <v>328.46</v>
+      </c>
+      <c r="R422" t="n">
+        <v>334.81</v>
+      </c>
+      <c r="S422" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="T422" t="n">
+        <v>342.99</v>
+      </c>
+      <c r="U422" t="n">
+        <v>335.61</v>
+      </c>
+      <c r="V422" t="n">
+        <v>245.48</v>
+      </c>
+      <c r="W422" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31877,7 +31952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B457"/>
+  <dimension ref="A1:B458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36450,6 +36525,16 @@
       </c>
       <c r="B457" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -36618,28 +36703,28 @@
         <v>0.0451</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2921450361795612</v>
+        <v>-0.2958993287270679</v>
       </c>
       <c r="J2" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K2" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01668898788094419</v>
+        <v>0.01719214700559468</v>
       </c>
       <c r="M2" t="n">
-        <v>11.64975232394362</v>
+        <v>11.64477641672143</v>
       </c>
       <c r="N2" t="n">
-        <v>245.906991877923</v>
+        <v>245.4522642473191</v>
       </c>
       <c r="O2" t="n">
-        <v>15.68142187041478</v>
+        <v>15.66691623285575</v>
       </c>
       <c r="P2" t="n">
-        <v>332.4746707207653</v>
+        <v>332.5192150171351</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36696,28 +36781,28 @@
         <v>0.0414</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.432163758183844</v>
+        <v>-0.4634240203458018</v>
       </c>
       <c r="J3" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01178618824108035</v>
+        <v>0.01344198715933642</v>
       </c>
       <c r="M3" t="n">
-        <v>18.70316546880488</v>
+        <v>18.86914459775434</v>
       </c>
       <c r="N3" t="n">
-        <v>765.7503146871206</v>
+        <v>772.9596332191441</v>
       </c>
       <c r="O3" t="n">
-        <v>27.6721938900247</v>
+        <v>27.80215159334155</v>
       </c>
       <c r="P3" t="n">
-        <v>335.57356609138</v>
+        <v>335.9445535151813</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36774,28 +36859,28 @@
         <v>0.0315</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.073175408584075</v>
+        <v>-1.09067597948427</v>
       </c>
       <c r="J4" t="n">
+        <v>421</v>
+      </c>
+      <c r="K4" t="n">
         <v>420</v>
       </c>
-      <c r="K4" t="n">
-        <v>419</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04246226828759936</v>
+        <v>0.04392712002415489</v>
       </c>
       <c r="M4" t="n">
-        <v>23.29250653363857</v>
+        <v>23.37912457904913</v>
       </c>
       <c r="N4" t="n">
-        <v>1270.898665022773</v>
+        <v>1270.568205243816</v>
       </c>
       <c r="O4" t="n">
-        <v>35.64966570702695</v>
+        <v>35.64503058273083</v>
       </c>
       <c r="P4" t="n">
-        <v>352.3859851596488</v>
+        <v>352.5934648718625</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36852,28 +36937,28 @@
         <v>0.0407</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.187480852360392</v>
+        <v>-2.192165340811018</v>
       </c>
       <c r="J5" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K5" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09753384990286307</v>
+        <v>0.09837596356494871</v>
       </c>
       <c r="M5" t="n">
-        <v>34.60357945740719</v>
+        <v>34.55231740590195</v>
       </c>
       <c r="N5" t="n">
-        <v>2231.765841718575</v>
+        <v>2226.314057616872</v>
       </c>
       <c r="O5" t="n">
-        <v>47.24156900144802</v>
+        <v>47.18383258719953</v>
       </c>
       <c r="P5" t="n">
-        <v>346.8964430552114</v>
+        <v>346.9512690310549</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36930,28 +37015,28 @@
         <v>0.043</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8469578151680544</v>
+        <v>-0.8635655443171043</v>
       </c>
       <c r="J6" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01958581981339647</v>
+        <v>0.0204213289136862</v>
       </c>
       <c r="M6" t="n">
-        <v>32.06306771549044</v>
+        <v>32.08671237102505</v>
       </c>
       <c r="N6" t="n">
-        <v>1785.096361850697</v>
+        <v>1783.241775256585</v>
       </c>
       <c r="O6" t="n">
-        <v>42.25040073006051</v>
+        <v>42.22844746443545</v>
       </c>
       <c r="P6" t="n">
-        <v>320.8876452671429</v>
+        <v>321.083863701858</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37008,28 +37093,28 @@
         <v>0.0547</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.919942078767134</v>
+        <v>-0.9282185618933815</v>
       </c>
       <c r="J7" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K7" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05570384310180709</v>
+        <v>0.05689817557586152</v>
       </c>
       <c r="M7" t="n">
-        <v>19.88304339073258</v>
+        <v>19.88645217517809</v>
       </c>
       <c r="N7" t="n">
-        <v>705.5052131733299</v>
+        <v>704.307346399323</v>
       </c>
       <c r="O7" t="n">
-        <v>26.56134810534529</v>
+        <v>26.5387894674818</v>
       </c>
       <c r="P7" t="n">
-        <v>325.253155317722</v>
+        <v>325.3512924334516</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37086,28 +37171,28 @@
         <v>0.0529</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.123534783780252</v>
+        <v>-0.132898573422308</v>
       </c>
       <c r="J8" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K8" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002142840312551741</v>
+        <v>0.002486093267728418</v>
       </c>
       <c r="M8" t="n">
-        <v>15.05001352823245</v>
+        <v>15.0698990414569</v>
       </c>
       <c r="N8" t="n">
-        <v>353.3980651410621</v>
+        <v>353.392200041544</v>
       </c>
       <c r="O8" t="n">
-        <v>18.79888467811487</v>
+        <v>18.79872868152376</v>
       </c>
       <c r="P8" t="n">
-        <v>310.1342157611265</v>
+        <v>310.2444268750364</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37164,28 +37249,28 @@
         <v>0.0423</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7449321352250174</v>
+        <v>-0.7636292083901732</v>
       </c>
       <c r="J9" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K9" t="n">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03018156069220035</v>
+        <v>0.03171137393515233</v>
       </c>
       <c r="M9" t="n">
-        <v>24.96673439990882</v>
+        <v>24.9974173633792</v>
       </c>
       <c r="N9" t="n">
-        <v>898.7219121158072</v>
+        <v>899.9122437513547</v>
       </c>
       <c r="O9" t="n">
-        <v>29.97869096734891</v>
+        <v>29.99853736020066</v>
       </c>
       <c r="P9" t="n">
-        <v>302.412186559109</v>
+        <v>302.6309361988394</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37242,28 +37327,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6519656644559287</v>
+        <v>-0.6661496324748539</v>
       </c>
       <c r="J10" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K10" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0187994529024037</v>
+        <v>0.01967669068296229</v>
       </c>
       <c r="M10" t="n">
-        <v>27.80579319132985</v>
+        <v>27.80696874853775</v>
       </c>
       <c r="N10" t="n">
-        <v>1104.474528855399</v>
+        <v>1103.74507361129</v>
       </c>
       <c r="O10" t="n">
-        <v>33.23363550464197</v>
+        <v>33.22265903884411</v>
       </c>
       <c r="P10" t="n">
-        <v>293.3369529571122</v>
+        <v>293.5037122792049</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37320,28 +37405,28 @@
         <v>0.0738</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3009741637281641</v>
+        <v>-0.3089266182114057</v>
       </c>
       <c r="J11" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K11" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01275833085259581</v>
+        <v>0.01347917013628119</v>
       </c>
       <c r="M11" t="n">
-        <v>15.49217485322479</v>
+        <v>15.49217656214867</v>
       </c>
       <c r="N11" t="n">
-        <v>348.8529213651889</v>
+        <v>348.6074966023182</v>
       </c>
       <c r="O11" t="n">
-        <v>18.67760480803652</v>
+        <v>18.67103362436901</v>
       </c>
       <c r="P11" t="n">
-        <v>295.7185590926601</v>
+        <v>295.8120192241357</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37398,28 +37483,28 @@
         <v>0.0559</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.335622877807994</v>
+        <v>-0.3437338661749946</v>
       </c>
       <c r="J12" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K12" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01220294106563458</v>
+        <v>0.01284091724652203</v>
       </c>
       <c r="M12" t="n">
-        <v>17.8563511227646</v>
+        <v>17.85356470986077</v>
       </c>
       <c r="N12" t="n">
-        <v>458.1301076626311</v>
+        <v>457.6557605928692</v>
       </c>
       <c r="O12" t="n">
-        <v>21.40397410909084</v>
+        <v>21.39289042165339</v>
       </c>
       <c r="P12" t="n">
-        <v>296.7380718514514</v>
+        <v>296.8328587714353</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37476,28 +37561,28 @@
         <v>0.0483</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4553338840295929</v>
+        <v>0.4561465589987928</v>
       </c>
       <c r="J13" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K13" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05040845401523053</v>
+        <v>0.05082766935780214</v>
       </c>
       <c r="M13" t="n">
-        <v>11.24682089234966</v>
+        <v>11.22404526549546</v>
       </c>
       <c r="N13" t="n">
-        <v>193.2138319593336</v>
+        <v>192.7611885461953</v>
       </c>
       <c r="O13" t="n">
-        <v>13.90013783958035</v>
+        <v>13.88384631671625</v>
       </c>
       <c r="P13" t="n">
-        <v>300.1744657504623</v>
+        <v>300.1648938802837</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37554,28 +37639,28 @@
         <v>0.0364</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3655178620230281</v>
+        <v>0.3652398909380761</v>
       </c>
       <c r="J14" t="n">
+        <v>421</v>
+      </c>
+      <c r="K14" t="n">
         <v>420</v>
       </c>
-      <c r="K14" t="n">
-        <v>419</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.02885855717535757</v>
+        <v>0.02897835299151208</v>
       </c>
       <c r="M14" t="n">
-        <v>11.76573475019548</v>
+        <v>11.73643390846328</v>
       </c>
       <c r="N14" t="n">
-        <v>222.9113919748064</v>
+        <v>222.2489572478947</v>
       </c>
       <c r="O14" t="n">
-        <v>14.93021741217476</v>
+        <v>14.90801654305142</v>
       </c>
       <c r="P14" t="n">
-        <v>301.6021672326353</v>
+        <v>301.6054039169708</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37632,28 +37717,28 @@
         <v>0.0495</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0348672476791829</v>
+        <v>0.03782807883348138</v>
       </c>
       <c r="J15" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K15" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0001782526804818829</v>
+        <v>0.0002108475889495143</v>
       </c>
       <c r="M15" t="n">
-        <v>14.45478866387311</v>
+        <v>14.43383360592938</v>
       </c>
       <c r="N15" t="n">
-        <v>339.5858447644006</v>
+        <v>338.8573126208185</v>
       </c>
       <c r="O15" t="n">
-        <v>18.42785513195718</v>
+        <v>18.4080773743707</v>
       </c>
       <c r="P15" t="n">
-        <v>292.8303483032582</v>
+        <v>292.7955906764215</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37710,28 +37795,28 @@
         <v>0.0485</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03869865266483985</v>
+        <v>0.03665992012578315</v>
       </c>
       <c r="J16" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K16" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0004283359976539058</v>
+        <v>0.0003863174347361609</v>
       </c>
       <c r="M16" t="n">
-        <v>9.81146514312973</v>
+        <v>9.798723990467471</v>
       </c>
       <c r="N16" t="n">
-        <v>172.491024912149</v>
+        <v>172.1179707292913</v>
       </c>
       <c r="O16" t="n">
-        <v>13.13358385636415</v>
+        <v>13.11937386955991</v>
       </c>
       <c r="P16" t="n">
-        <v>314.9371452731311</v>
+        <v>314.9612441862805</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37788,28 +37873,28 @@
         <v>0.0534</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06051466043777787</v>
+        <v>0.06201709375834781</v>
       </c>
       <c r="J17" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K17" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L17" t="n">
-        <v>0.001446668328936473</v>
+        <v>0.001526914366295817</v>
       </c>
       <c r="M17" t="n">
-        <v>8.50982696835162</v>
+        <v>8.497396962170441</v>
       </c>
       <c r="N17" t="n">
-        <v>125.045568510228</v>
+        <v>124.7700698742011</v>
       </c>
       <c r="O17" t="n">
-        <v>11.18237758753603</v>
+        <v>11.17005236667228</v>
       </c>
       <c r="P17" t="n">
-        <v>323.8115392228303</v>
+        <v>323.7938432222871</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37866,28 +37951,28 @@
         <v>0.0569</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.00433867399170521</v>
+        <v>-0.00186753016560345</v>
       </c>
       <c r="J18" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K18" t="n">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L18" t="n">
-        <v>9.644011813914055e-06</v>
+        <v>1.795025331596811e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>7.478448585780516</v>
+        <v>7.473017496835936</v>
       </c>
       <c r="N18" t="n">
-        <v>96.45495435654801</v>
+        <v>96.28298473191334</v>
       </c>
       <c r="O18" t="n">
-        <v>9.821148321685607</v>
+        <v>9.812389348772976</v>
       </c>
       <c r="P18" t="n">
-        <v>329.9729887705365</v>
+        <v>329.9438204717396</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -37944,28 +38029,28 @@
         <v>0.0371</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1104127516031745</v>
+        <v>-0.1060493254882668</v>
       </c>
       <c r="J19" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K19" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L19" t="n">
-        <v>0.004678554293586545</v>
+        <v>0.004333889338359098</v>
       </c>
       <c r="M19" t="n">
-        <v>8.864901232927039</v>
+        <v>8.861885951163814</v>
       </c>
       <c r="N19" t="n">
-        <v>128.3024551367982</v>
+        <v>128.1792259287246</v>
       </c>
       <c r="O19" t="n">
-        <v>11.32706736701068</v>
+        <v>11.32162647011129</v>
       </c>
       <c r="P19" t="n">
-        <v>344.6671824087929</v>
+        <v>344.6157889859753</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -38022,28 +38107,28 @@
         <v>0.0605</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1525730318210455</v>
+        <v>0.1504361834162102</v>
       </c>
       <c r="J20" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K20" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L20" t="n">
-        <v>0.008884993199697933</v>
+        <v>0.008685472066288558</v>
       </c>
       <c r="M20" t="n">
-        <v>8.362862391048703</v>
+        <v>8.343500953948222</v>
       </c>
       <c r="N20" t="n">
-        <v>128.4598225029443</v>
+        <v>128.1411367874957</v>
       </c>
       <c r="O20" t="n">
-        <v>11.33401175678516</v>
+        <v>11.31994420425718</v>
       </c>
       <c r="P20" t="n">
-        <v>340.8590248454461</v>
+        <v>340.8841697752372</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -38100,28 +38185,28 @@
         <v>0.1018</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3144244935299608</v>
+        <v>-0.3163414608980514</v>
       </c>
       <c r="J21" t="n">
+        <v>421</v>
+      </c>
+      <c r="K21" t="n">
         <v>420</v>
       </c>
-      <c r="K21" t="n">
-        <v>419</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.03157212027611778</v>
+        <v>0.03209954287947003</v>
       </c>
       <c r="M21" t="n">
-        <v>9.022257876011896</v>
+        <v>9.011046198241914</v>
       </c>
       <c r="N21" t="n">
-        <v>149.7265939002657</v>
+        <v>149.4050708602022</v>
       </c>
       <c r="O21" t="n">
-        <v>12.23628186583922</v>
+        <v>12.22313670299904</v>
       </c>
       <c r="P21" t="n">
-        <v>347.9290574877379</v>
+        <v>347.9516771199885</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -38178,28 +38263,28 @@
         <v>0.0604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.259752804083208</v>
+        <v>-0.2979194745084149</v>
       </c>
       <c r="J22" t="n">
+        <v>421</v>
+      </c>
+      <c r="K22" t="n">
         <v>420</v>
       </c>
-      <c r="K22" t="n">
-        <v>419</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.01459588759788766</v>
+        <v>0.01814170195096187</v>
       </c>
       <c r="M22" t="n">
-        <v>10.26447696623621</v>
+        <v>10.48755441186897</v>
       </c>
       <c r="N22" t="n">
-        <v>224.9090955658867</v>
+        <v>237.8427033940225</v>
       </c>
       <c r="O22" t="n">
-        <v>14.99696954607452</v>
+        <v>15.42214976564624</v>
       </c>
       <c r="P22" t="n">
-        <v>339.0900797125933</v>
+        <v>339.540536131428</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -38237,7 +38322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W421"/>
+  <dimension ref="A1:W422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87029,27 +87114,27 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>-37.68453150526895,174.81241924293866</t>
+          <t>-37.68456044604945,174.8123280596198</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>-37.68395511686227,174.81182218206578</t>
+          <t>-37.68398034781443,174.81174268664842</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>-37.683259618253246,174.81160038252065</t>
+          <t>-37.68328123993947,174.81153225922893</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>-37.68255221709779,174.8114160645669</t>
+          <t>-37.6825757101543,174.81134204564398</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>-37.681964246583526,174.8108554404452</t>
+          <t>-37.68197834893404,174.8108110082928</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -87084,7 +87169,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t>-37.6774660271232,174.80814677299674</t>
+          <t>-37.6774550395533,174.80818226766712</t>
         </is>
       </c>
       <c r="O421" t="inlineStr">
@@ -87114,7 +87199,7 @@
       </c>
       <c r="T421" t="inlineStr">
         <is>
-          <t>-37.6734929713654,174.8062317753166</t>
+          <t>-37.67348618811989,174.80625677210264</t>
         </is>
       </c>
       <c r="U421" t="inlineStr">
@@ -87124,10 +87209,127 @@
       </c>
       <c r="V421" t="inlineStr">
         <is>
-          <t>-37.67173044456345,174.80666324382523</t>
+          <t>-37.67177061597986,174.80656101401323</t>
         </is>
       </c>
       <c r="W421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-37.68541808094491,174.81203897320987</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-37.68454076231594,174.8123900769197</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-37.683970923809284,174.81177237898302</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-37.68327793152321,174.81154268304283</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-37.68256688773158,174.81136984222954</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-37.68197781424805,174.8108126929245</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-37.68134146796874,174.81040831791935</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-37.68053802337977,174.81054383094164</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-37.67988265328423,174.81020380877436</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-37.67929706579212,174.80962959443937</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-37.67863030484067,174.80931758259962</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-37.678104089238055,174.80855153229683</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-37.67743901599511,174.80823403070863</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-37.67673438247494,174.80807570483182</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-37.67611179874304,174.80766505174174</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-37.675482506187144,174.8072277161491</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>-37.674819394369855,174.806898316664</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>-37.674181607704085,174.8064683039023</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>-37.67347792012265,174.80628724028182</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>-37.67277291171339,174.80606148932802</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>-37.671761830985616,174.80658337044298</t>
+        </is>
+      </c>
+      <c r="W422" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
